--- a/Hoadon/HD2026/HDVao/2/3502550210_HDDienTuKhongMa.xlsx
+++ b/Hoadon/HD2026/HDVao/2/3502550210_HDDienTuKhongMa.xlsx
@@ -699,6 +699,89 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>K26TAA</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>24/02/2026</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="n">
+        <v>3700315.0</v>
+      </c>
+      <c r="L12" s="13" t="n">
+        <v>296025.0</v>
+      </c>
+      <c r="M12" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13" t="n">
+        <v>3996340.0</v>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:S3"/>
